--- a/web/public/forms/gy-hadogeup.xlsx
+++ b/web/public/forms/gy-hadogeup.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공사 하도급계약서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'공사 하도급계약서'!$A$1:$X$80</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'공사 하도급계약서'!$A$1:$X$87</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +20,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="&quot;₩&quot;#,##0&quot; (부가세 포함)&quot;;;&quot;&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;원 (계약금액에 포함)&quot;;;&quot;&quot;"/>
+    <numFmt numFmtId="166" formatCode="yyyy&quot;년&quot; m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,32 +38,59 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000F203F"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="006B7280"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="00111827"/>
       <sz val="19"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -65,12 +99,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F8FC"/>
+        <fgColor rgb="00F3F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF3FB"/>
+        <fgColor rgb="00EEF4FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8EEF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,23 +123,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </left>
       <right style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </right>
       <top style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,35 +148,59 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X83"/>
+  <dimension ref="A1:X90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.6" customWidth="1" min="1" max="1"/>
@@ -533,15 +596,15 @@
     <col width="3.6" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵   |   k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다   </t>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
         </is>
       </c>
     </row>
@@ -565,7 +628,7 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
@@ -595,7 +658,7 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
@@ -625,7 +688,7 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
@@ -655,7 +718,7 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
@@ -685,7 +748,7 @@
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="G9" s="7" t="n"/>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
@@ -715,7 +778,10 @@
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="inlineStr"/>
+      <c r="G10" s="8">
+        <f>IF(N(G9)=0,"",G9-ROUND(G9/1.1,0))</f>
+        <v/>
+      </c>
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
@@ -745,7 +811,7 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="n"/>
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
@@ -775,7 +841,7 @@
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="n"/>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
@@ -805,7 +871,7 @@
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="n"/>
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
@@ -824,7 +890,7 @@
       <c r="W13" s="5" t="n"/>
       <c r="X13" s="5" t="n"/>
     </row>
-    <row r="14" ht="24" customHeight="1">
+    <row r="14" ht="34" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  지급 방법(현금/어음)</t>
@@ -835,7 +901,7 @@
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="n"/>
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
@@ -865,7 +931,7 @@
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="n"/>
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="n"/>
       <c r="J15" s="5" t="n"/>
@@ -895,7 +961,7 @@
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="n"/>
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
@@ -925,7 +991,7 @@
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="n"/>
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
@@ -955,7 +1021,7 @@
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
-      <c r="G18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="n"/>
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
@@ -975,8 +1041,8 @@
       <c r="X18" s="5" t="n"/>
     </row>
     <row r="19" ht="6" customHeight="1"/>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>원사업자(이하 「갑」)와 수급사업자(이하 「을」)는 위 공사에 관하여 다음과 같이 하도급계약을 체결한다.</t>
         </is>
@@ -984,14 +1050,14 @@
     </row>
     <row r="21" ht="6" customHeight="1"/>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>제1조 (위탁 내용)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="43.5" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>갑은 위 공사 중 별첨 내역서에 적은 부분을 을에게 위탁하고, 을은 설계도서·시방서 및 이 계약에 따라 이를 시공한다.</t>
         </is>
@@ -999,14 +1065,14 @@
     </row>
     <row r="24" ht="4" customHeight="1"/>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>제2조 (하도급대금)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>하도급대금은 위에 적은 금액으로 하며 부가가치세의 포함 여부는 위 표에 따른다. 갑은 정당한 사유 없이 하도급대금을 부당하게 감액하지 아니한다.</t>
         </is>
@@ -1014,14 +1080,14 @@
     </row>
     <row r="27" ht="4" customHeight="1"/>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>제3조 (대금의 지급)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>갑은 목적물의 수령일부터 위 지급기한 안에 하도급대금을 지급한다. 어음으로 지급하는 경우 만기는 관계 법령이 정한 기간을 넘지 아니하며, 그 기간을 넘는 부분에 대하여는 법정 할인료를 지급한다.</t>
         </is>
@@ -1029,437 +1095,1559 @@
     </row>
     <row r="30" ht="4" customHeight="1"/>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>제4조 (발주자로부터 받은 대금의 지급)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="43.5" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>갑이 발주자로부터 기성금 또는 준공금을 받은 때에는 그 내용과 비율에 따라 정해진 기간 안에 을에게 지급한다.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="4" customHeight="1"/>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="1" t="inlineStr">
+    <row r="34" ht="6.333333333333333" customHeight="1"/>
+    <row r="35" ht="6.333333333333333" customHeight="1"/>
+    <row r="36" ht="6.333333333333333" customHeight="1"/>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>제5조 (검사)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="43.5" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="38" ht="43.5" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>갑은 을이 시공을 마친 부분에 대하여 위 표에 적은 방법과 시기에 따라 검사하고 그 결과를 을에게 서면으로 통지한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="4" customHeight="1"/>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>제6조 (설계변경 등에 따른 조정)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="43.5" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>설계변경·물가변동 등으로 원도급 계약금액이 조정된 때에는 갑은 그 내용과 비율에 따라 하도급대금을 조정한다.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="4" customHeight="1"/>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>제7조 (자재의 공급)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="58" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>갑이 자재를 공급하는 경우 그 품목·수량·단가·공급 시기를 별도로 정한다. 갑은 정당한 사유 없이 자기가 지정한 물품을 을에게 강제로 구입하게 하지 아니한다.</t>
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>제6조 (설계변경 등에 따른 조정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="43.5" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>설계변경·물가변동 등으로 원도급 계약금액이 조정된 때에는 갑은 그 내용과 비율에 따라 하도급대금을 조정한다.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="4" customHeight="1"/>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>제8조 (안전보건)</t>
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>제7조 (자재의 공급)</t>
         </is>
       </c>
     </row>
     <row r="44" ht="58" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>갑과 을은 산업안전보건 관계 법령을 지킨다. 갑은 안전보건 협의체를 운영하고 을은 이에 참여한다. 을은 소속 근로자의 산재보험·고용보험 가입 증명을 갑에게 제출한다.</t>
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>갑이 자재를 공급하는 경우 그 품목·수량·단가·공급 시기를 별도로 정한다. 갑은 정당한 사유 없이 자기가 지정한 물품을 을에게 강제로 구입하게 하지 아니한다.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="4" customHeight="1"/>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>제9조 (하도급대금 지급보증과 계약이행보증)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="43.5" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>갑은 하도급대금 지급보증서를 을에게 주고, 을은 계약이행보증서를 갑에게 준다. 다만 관계 법령에서 면제되는 경우에는 그러하지 아니하다.</t>
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>제8조 (안전보건)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>갑과 을은 산업안전보건 관계 법령을 지킨다. 갑은 안전보건 협의체를 운영하고 을은 이에 참여한다. 을은 소속 근로자의 산재보험·고용보험 가입 증명을 갑에게 제출한다.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="4" customHeight="1"/>
     <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>제10조 (재하도급의 제한)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="29" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>을은 갑의 서면 승낙 없이 이 계약의 공사를 다시 하도급할 수 없다.</t>
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>제9조 (하도급대금 지급보증과 계약이행보증)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="43.5" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>갑은 하도급대금 지급보증서를 을에게 주고, 을은 계약이행보증서를 갑에게 준다. 다만 관계 법령에서 면제되는 경우에는 그러하지 아니하다.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="4" customHeight="1"/>
     <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>제11조 (지체상금)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="43.5" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>을의 책임 있는 사유로 공사가 지연된 때에는 지체일수에 하도급대금과 위 지체상금률을 곱한 금액을 갑에게 지급한다.</t>
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>제10조 (재하도급의 제한)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="29" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>을은 갑의 서면 승낙 없이 이 계약의 공사를 다시 하도급할 수 없다.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="4" customHeight="1"/>
     <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>제12조 (하자담보책임)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="29" customHeight="1">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>을은 목적물 인도일부터 위 기간 동안 시공상 하자를 무상으로 보수한다.</t>
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>제11조 (지체상금)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="43.5" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>을의 책임 있는 사유로 공사가 지연된 때에는 지체일수에 하도급대금과 위 지체상금률을 곱한 금액을 갑에게 지급한다.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="4" customHeight="1"/>
     <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>제13조 (계약의 해제·해지)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="43.5" customHeight="1">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>상대방이 이 계약을 위반하여 서면으로 최고하였음에도 상당한 기간 안에 시정하지 아니한 때에는 계약을 해제 또는 해지할 수 있다.</t>
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>제12조 (하자담보책임)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="29" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>을은 목적물 인도일부터 위 기간 동안 시공상 하자를 무상으로 보수한다.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="4" customHeight="1"/>
     <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t>제14조 (분쟁의 해결)</t>
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>제13조 (계약의 해제·해지)</t>
         </is>
       </c>
     </row>
     <row r="62" ht="43.5" customHeight="1">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>이 계약에 관한 분쟁은 협의로 해결하되, 협의가 되지 아니한 때에는 하도급분쟁조정협의회의 조정 또는 관할 법원의 판결에 따른다.</t>
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>상대방이 이 계약을 위반하여 서면으로 최고하였음에도 상당한 기간 안에 시정하지 아니한 때에는 계약을 해제 또는 해지할 수 있다.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="4" customHeight="1"/>
     <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="1" t="inlineStr">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>제14조 (분쟁의 해결)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="43.5" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>이 계약에 관한 분쟁은 협의로 해결하되, 협의가 되지 아니한 때에는 하도급분쟁조정협의회의 조정 또는 관할 법원의 판결에 따른다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="4" customHeight="1"/>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>제15조 (특약사항)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="43.5" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
+    <row r="68" ht="43.5" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">                                                                 </t>
         </is>
       </c>
     </row>
-    <row r="66" ht="4" customHeight="1"/>
-    <row r="67" ht="6" customHeight="1"/>
-    <row r="68" ht="26" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
+    <row r="69" ht="4" customHeight="1"/>
+    <row r="70" ht="6" customHeight="1"/>
+    <row r="71" ht="7.291666666666686" customHeight="1"/>
+    <row r="72" ht="7.291666666666686" customHeight="1"/>
+    <row r="73" ht="7.291666666666686" customHeight="1"/>
+    <row r="74" ht="7.291666666666686" customHeight="1"/>
+    <row r="75" ht="34" customHeight="1">
+      <c r="A75" s="9" t="inlineStr">
         <is>
           <t>이 계약을 증명하기 위하여 계약서 2통을 작성하여 갑과 을이 각각 기명날인한 후 1통씩 보관한다.</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="6" customHeight="1"/>
-    <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="9" t="inlineStr">
+    <row r="76" ht="6" customHeight="1"/>
+    <row r="77" ht="24" customHeight="1">
+      <c r="A77" s="12" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B70" s="5" t="n"/>
-      <c r="C70" s="9" t="inlineStr">
+      <c r="B77" s="5" t="n"/>
+      <c r="C77" s="12" t="inlineStr">
         <is>
           <t>상호(성명)</t>
         </is>
       </c>
-      <c r="D70" s="5" t="n"/>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="n"/>
-      <c r="G70" s="5" t="n"/>
-      <c r="H70" s="9" t="inlineStr">
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="n"/>
+      <c r="G77" s="5" t="n"/>
+      <c r="H77" s="12" t="inlineStr">
         <is>
           <t>사업자등록번호</t>
         </is>
       </c>
-      <c r="I70" s="5" t="n"/>
-      <c r="J70" s="5" t="n"/>
-      <c r="K70" s="5" t="n"/>
-      <c r="L70" s="9" t="inlineStr">
+      <c r="I77" s="5" t="n"/>
+      <c r="J77" s="5" t="n"/>
+      <c r="K77" s="5" t="n"/>
+      <c r="L77" s="12" t="inlineStr">
         <is>
           <t>대표자</t>
         </is>
       </c>
-      <c r="M70" s="5" t="n"/>
-      <c r="N70" s="5" t="n"/>
-      <c r="O70" s="9" t="inlineStr">
+      <c r="M77" s="5" t="n"/>
+      <c r="N77" s="5" t="n"/>
+      <c r="O77" s="12" t="inlineStr">
         <is>
           <t>주소</t>
         </is>
       </c>
-      <c r="P70" s="5" t="n"/>
-      <c r="Q70" s="5" t="n"/>
-      <c r="R70" s="5" t="n"/>
-      <c r="S70" s="5" t="n"/>
-      <c r="T70" s="5" t="n"/>
-      <c r="U70" s="5" t="n"/>
-      <c r="V70" s="9" t="inlineStr">
+      <c r="P77" s="5" t="n"/>
+      <c r="Q77" s="5" t="n"/>
+      <c r="R77" s="5" t="n"/>
+      <c r="S77" s="5" t="n"/>
+      <c r="T77" s="5" t="n"/>
+      <c r="U77" s="5" t="n"/>
+      <c r="V77" s="12" t="inlineStr">
         <is>
           <t>연락처</t>
         </is>
       </c>
-      <c r="W70" s="5" t="n"/>
-      <c r="X70" s="5" t="n"/>
-    </row>
-    <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="10" t="inlineStr"/>
-      <c r="B71" s="5" t="n"/>
-      <c r="C71" s="10" t="inlineStr"/>
-      <c r="D71" s="5" t="n"/>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="n"/>
-      <c r="G71" s="5" t="n"/>
-      <c r="H71" s="10" t="inlineStr"/>
-      <c r="I71" s="5" t="n"/>
-      <c r="J71" s="5" t="n"/>
-      <c r="K71" s="5" t="n"/>
-      <c r="L71" s="10" t="inlineStr"/>
-      <c r="M71" s="5" t="n"/>
-      <c r="N71" s="5" t="n"/>
-      <c r="O71" s="10" t="inlineStr"/>
-      <c r="P71" s="5" t="n"/>
-      <c r="Q71" s="5" t="n"/>
-      <c r="R71" s="5" t="n"/>
-      <c r="S71" s="5" t="n"/>
-      <c r="T71" s="5" t="n"/>
-      <c r="U71" s="5" t="n"/>
-      <c r="V71" s="10" t="inlineStr"/>
-      <c r="W71" s="5" t="n"/>
-      <c r="X71" s="5" t="n"/>
-    </row>
-    <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="10" t="inlineStr"/>
-      <c r="B72" s="5" t="n"/>
-      <c r="C72" s="10" t="inlineStr"/>
-      <c r="D72" s="5" t="n"/>
-      <c r="E72" s="5" t="n"/>
-      <c r="F72" s="5" t="n"/>
-      <c r="G72" s="5" t="n"/>
-      <c r="H72" s="10" t="inlineStr"/>
-      <c r="I72" s="5" t="n"/>
-      <c r="J72" s="5" t="n"/>
-      <c r="K72" s="5" t="n"/>
-      <c r="L72" s="10" t="inlineStr"/>
-      <c r="M72" s="5" t="n"/>
-      <c r="N72" s="5" t="n"/>
-      <c r="O72" s="10" t="inlineStr"/>
-      <c r="P72" s="5" t="n"/>
-      <c r="Q72" s="5" t="n"/>
-      <c r="R72" s="5" t="n"/>
-      <c r="S72" s="5" t="n"/>
-      <c r="T72" s="5" t="n"/>
-      <c r="U72" s="5" t="n"/>
-      <c r="V72" s="10" t="inlineStr"/>
-      <c r="W72" s="5" t="n"/>
-      <c r="X72" s="5" t="n"/>
-    </row>
-    <row r="73" ht="6" customHeight="1"/>
-    <row r="74" ht="26" customHeight="1">
-      <c r="A74" s="7" t="inlineStr">
+      <c r="W77" s="5" t="n"/>
+      <c r="X77" s="5" t="n"/>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>갑</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n"/>
+      <c r="C78" s="13" t="n"/>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="13" t="n"/>
+      <c r="I78" s="5" t="n"/>
+      <c r="J78" s="5" t="n"/>
+      <c r="K78" s="5" t="n"/>
+      <c r="L78" s="13" t="n"/>
+      <c r="M78" s="5" t="n"/>
+      <c r="N78" s="5" t="n"/>
+      <c r="O78" s="14" t="n"/>
+      <c r="P78" s="5" t="n"/>
+      <c r="Q78" s="5" t="n"/>
+      <c r="R78" s="5" t="n"/>
+      <c r="S78" s="5" t="n"/>
+      <c r="T78" s="5" t="n"/>
+      <c r="U78" s="5" t="n"/>
+      <c r="V78" s="13" t="n"/>
+      <c r="W78" s="5" t="n"/>
+      <c r="X78" s="5" t="n"/>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>을</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n"/>
+      <c r="C79" s="13" t="n"/>
+      <c r="D79" s="5" t="n"/>
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="5" t="n"/>
+      <c r="G79" s="5" t="n"/>
+      <c r="H79" s="13" t="n"/>
+      <c r="I79" s="5" t="n"/>
+      <c r="J79" s="5" t="n"/>
+      <c r="K79" s="5" t="n"/>
+      <c r="L79" s="13" t="n"/>
+      <c r="M79" s="5" t="n"/>
+      <c r="N79" s="5" t="n"/>
+      <c r="O79" s="14" t="n"/>
+      <c r="P79" s="5" t="n"/>
+      <c r="Q79" s="5" t="n"/>
+      <c r="R79" s="5" t="n"/>
+      <c r="S79" s="5" t="n"/>
+      <c r="T79" s="5" t="n"/>
+      <c r="U79" s="5" t="n"/>
+      <c r="V79" s="13" t="n"/>
+      <c r="W79" s="5" t="n"/>
+      <c r="X79" s="5" t="n"/>
+    </row>
+    <row r="80" ht="6" customHeight="1"/>
+    <row r="81" ht="34" customHeight="1">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>※ 이 계약서는 일반 양식입니다. 실제 체결 전에 반드시 검토를 받으시고, 정부가 고시한 표준계약서가 있는 계약은 그 원문을 사용하시는 편이 안전합니다.</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="6" customHeight="1"/>
-    <row r="76" ht="10" customHeight="1"/>
-    <row r="77" ht="26" customHeight="1">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t>년        월        일</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="K78" s="12" t="inlineStr">
+    <row r="82" ht="6" customHeight="1"/>
+    <row r="83" ht="10" customHeight="1"/>
+    <row r="84" ht="26" customHeight="1">
+      <c r="A84" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년        월        일</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="24" customHeight="1">
+      <c r="A85" s="16" t="inlineStr"/>
+      <c r="K85" s="17" t="inlineStr">
         <is>
           <t>갑 (원사업자)</t>
         </is>
       </c>
-      <c r="S78" s="11" t="inlineStr">
+      <c r="Q85" s="18" t="n"/>
+      <c r="U85" s="19" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="K79" s="12" t="inlineStr">
+    <row r="86" ht="24" customHeight="1">
+      <c r="A86" s="16" t="inlineStr"/>
+      <c r="K86" s="17" t="inlineStr">
         <is>
           <t>을 (수급사업자)</t>
         </is>
       </c>
-      <c r="S79" s="11" t="inlineStr">
+      <c r="Q86" s="18" t="n"/>
+      <c r="U86" s="19" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="6" customHeight="1"/>
-    <row r="83">
-      <c r="A83" s="13" t="inlineStr">
-        <is>
-          <t>발주기관이 정한 서식이 있으면 그 서식을 사용하세요. 이 줄과 1행은 인쇄 전에 지우셔도 됩니다.</t>
+    <row r="87" ht="6" customHeight="1"/>
+    <row r="89" ht="34" customHeight="1">
+      <c r="A89" s="20" t="inlineStr">
+        <is>
+          <t>노란 칸 = 요율·기준값(발주기관 기준으로 고쳐 씀) · 옅은 하늘색 칸 = 자동 계산(지우지 마세요) · 뒤 시트에 «작성 예시» 가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="19.5" customHeight="1">
+      <c r="A90" s="20" t="inlineStr">
+        <is>
+          <t>발주기관이 정한 서식이 있으면 그 서식을 쓰세요. 이 줄과 1행은 지워도 됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="88">
+  <mergeCells count="93">
+    <mergeCell ref="K85:P85"/>
+    <mergeCell ref="Q86:T86"/>
     <mergeCell ref="G10:X10"/>
+    <mergeCell ref="A75:X75"/>
     <mergeCell ref="G18:X18"/>
-    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="K86:P86"/>
     <mergeCell ref="A3:X3"/>
     <mergeCell ref="A55:X55"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A32:X32"/>
     <mergeCell ref="A29:X29"/>
     <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A81:X81"/>
     <mergeCell ref="A38:X38"/>
-    <mergeCell ref="S79:X79"/>
-    <mergeCell ref="C71:G71"/>
     <mergeCell ref="A31:X31"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A58:X58"/>
     <mergeCell ref="A40:X40"/>
+    <mergeCell ref="A67:X67"/>
     <mergeCell ref="G12:X12"/>
-    <mergeCell ref="H72:K72"/>
+    <mergeCell ref="H79:K79"/>
+    <mergeCell ref="V78:X78"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="L71:N71"/>
-    <mergeCell ref="O71:U71"/>
+    <mergeCell ref="C77:G77"/>
     <mergeCell ref="G7:X7"/>
     <mergeCell ref="A25:X25"/>
     <mergeCell ref="A18:F18"/>
-    <mergeCell ref="H71:K71"/>
+    <mergeCell ref="A84:X84"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="U85:X85"/>
     <mergeCell ref="A50:X50"/>
     <mergeCell ref="A47:X47"/>
+    <mergeCell ref="O77:U77"/>
     <mergeCell ref="A22:X22"/>
     <mergeCell ref="G16:X16"/>
     <mergeCell ref="A20:X20"/>
-    <mergeCell ref="A71:B71"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A28:X28"/>
+    <mergeCell ref="L77:N77"/>
     <mergeCell ref="G9:X9"/>
     <mergeCell ref="A44:X44"/>
-    <mergeCell ref="C70:G70"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A59:X59"/>
     <mergeCell ref="G11:X11"/>
     <mergeCell ref="A64:X64"/>
-    <mergeCell ref="V72:X72"/>
+    <mergeCell ref="A86:J86"/>
+    <mergeCell ref="L78:N78"/>
     <mergeCell ref="A61:X61"/>
-    <mergeCell ref="K78:R78"/>
-    <mergeCell ref="O70:U70"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="O79:U79"/>
     <mergeCell ref="A41:X41"/>
+    <mergeCell ref="A90:X90"/>
     <mergeCell ref="G13:X13"/>
-    <mergeCell ref="A74:X74"/>
     <mergeCell ref="A56:X56"/>
-    <mergeCell ref="K79:R79"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="L79:N79"/>
     <mergeCell ref="G15:X15"/>
-    <mergeCell ref="V70:X70"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A53:X53"/>
-    <mergeCell ref="A35:X35"/>
     <mergeCell ref="A62:X62"/>
-    <mergeCell ref="V71:X71"/>
     <mergeCell ref="A68:X68"/>
-    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="U86:X86"/>
+    <mergeCell ref="Q85:T85"/>
     <mergeCell ref="G17:X17"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="V77:X77"/>
+    <mergeCell ref="A85:J85"/>
     <mergeCell ref="A65:X65"/>
+    <mergeCell ref="H77:K77"/>
     <mergeCell ref="G6:X6"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A37:X37"/>
     <mergeCell ref="A46:X46"/>
-    <mergeCell ref="S78:X78"/>
-    <mergeCell ref="O72:U72"/>
+    <mergeCell ref="A89:X89"/>
+    <mergeCell ref="C79:G79"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A26:X26"/>
     <mergeCell ref="G5:X5"/>
+    <mergeCell ref="O78:U78"/>
     <mergeCell ref="G14:X14"/>
+    <mergeCell ref="H78:K78"/>
     <mergeCell ref="A23:X23"/>
-    <mergeCell ref="L72:N72"/>
     <mergeCell ref="A43:X43"/>
     <mergeCell ref="A52:X52"/>
-    <mergeCell ref="L70:N70"/>
-    <mergeCell ref="A77:X77"/>
-    <mergeCell ref="A34:X34"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="H70:K70"/>
-    <mergeCell ref="A83:X83"/>
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="V79:X79"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A49:X49"/>
     <mergeCell ref="M1:X1"/>
     <mergeCell ref="G8:X8"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:X89"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.6" customWidth="1" min="1" max="1"/>
+    <col width="3.6" customWidth="1" min="2" max="2"/>
+    <col width="3.6" customWidth="1" min="3" max="3"/>
+    <col width="3.6" customWidth="1" min="4" max="4"/>
+    <col width="3.6" customWidth="1" min="5" max="5"/>
+    <col width="3.6" customWidth="1" min="6" max="6"/>
+    <col width="3.6" customWidth="1" min="7" max="7"/>
+    <col width="3.6" customWidth="1" min="8" max="8"/>
+    <col width="3.6" customWidth="1" min="9" max="9"/>
+    <col width="3.6" customWidth="1" min="10" max="10"/>
+    <col width="3.6" customWidth="1" min="11" max="11"/>
+    <col width="3.6" customWidth="1" min="12" max="12"/>
+    <col width="3.6" customWidth="1" min="13" max="13"/>
+    <col width="3.6" customWidth="1" min="14" max="14"/>
+    <col width="3.6" customWidth="1" min="15" max="15"/>
+    <col width="3.6" customWidth="1" min="16" max="16"/>
+    <col width="3.6" customWidth="1" min="17" max="17"/>
+    <col width="3.6" customWidth="1" min="18" max="18"/>
+    <col width="3.6" customWidth="1" min="19" max="19"/>
+    <col width="3.6" customWidth="1" min="20" max="20"/>
+    <col width="3.6" customWidth="1" min="21" max="21"/>
+    <col width="3.6" customWidth="1" min="22" max="22"/>
+    <col width="3.6" customWidth="1" min="23" max="23"/>
+    <col width="3.6" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="M1" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>공 사 하 도 급 계 약 서</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  원도급 공사명</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  하도급 공사명</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사 중 구조물공(암거)</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공사 장소</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>가나시 다라동 123-4 일원</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="n"/>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  하도급 공사기간</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>2026. 5. 1. ~ 2026. 10. 31.</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="5" t="n"/>
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  하도급대금</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="7" t="n">
+        <v>285000000</v>
+      </c>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
+      <c r="Q9" s="5" t="n"/>
+      <c r="R9" s="5" t="n"/>
+      <c r="S9" s="5" t="n"/>
+      <c r="T9" s="5" t="n"/>
+      <c r="U9" s="5" t="n"/>
+      <c r="V9" s="5" t="n"/>
+      <c r="W9" s="5" t="n"/>
+      <c r="X9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  부가가치세</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="8">
+        <f>IF(N(G9)=0,"",G9-ROUND(G9/1.1,0))</f>
+        <v/>
+      </c>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
+      <c r="Q10" s="5" t="n"/>
+      <c r="R10" s="5" t="n"/>
+      <c r="S10" s="5" t="n"/>
+      <c r="T10" s="5" t="n"/>
+      <c r="U10" s="5" t="n"/>
+      <c r="V10" s="5" t="n"/>
+      <c r="W10" s="5" t="n"/>
+      <c r="X10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  선급금</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>원사업자가 받은 선금 비율만큼, 받은 날부터 15일 안에 지급</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
+      <c r="Q11" s="5" t="n"/>
+      <c r="R11" s="5" t="n"/>
+      <c r="S11" s="5" t="n"/>
+      <c r="T11" s="5" t="n"/>
+      <c r="U11" s="5" t="n"/>
+      <c r="V11" s="5" t="n"/>
+      <c r="W11" s="5" t="n"/>
+      <c r="X11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  기성 지급 주기</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>월 1회</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
+      <c r="Q12" s="5" t="n"/>
+      <c r="R12" s="5" t="n"/>
+      <c r="S12" s="5" t="n"/>
+      <c r="T12" s="5" t="n"/>
+      <c r="U12" s="5" t="n"/>
+      <c r="V12" s="5" t="n"/>
+      <c r="W12" s="5" t="n"/>
+      <c r="X12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  대금 지급기한</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>원사업자가 기성금을 받은 날부터 15일 안</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
+      <c r="Q13" s="5" t="n"/>
+      <c r="R13" s="5" t="n"/>
+      <c r="S13" s="5" t="n"/>
+      <c r="T13" s="5" t="n"/>
+      <c r="U13" s="5" t="n"/>
+      <c r="V13" s="5" t="n"/>
+      <c r="W13" s="5" t="n"/>
+      <c r="X13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  지급 방법(현금/어음)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>현금(하도급지킴이)</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
+      <c r="Q14" s="5" t="n"/>
+      <c r="R14" s="5" t="n"/>
+      <c r="S14" s="5" t="n"/>
+      <c r="T14" s="5" t="n"/>
+      <c r="U14" s="5" t="n"/>
+      <c r="V14" s="5" t="n"/>
+      <c r="W14" s="5" t="n"/>
+      <c r="X14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  계약이행보증</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>하도급대금의 10% (보증서)</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
+      <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="5" t="n"/>
+      <c r="T15" s="5" t="n"/>
+      <c r="U15" s="5" t="n"/>
+      <c r="V15" s="5" t="n"/>
+      <c r="W15" s="5" t="n"/>
+      <c r="X15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  하도급대금 지급보증</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>건설공제조합 지급보증서 교부</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
+      <c r="Q16" s="5" t="n"/>
+      <c r="R16" s="5" t="n"/>
+      <c r="S16" s="5" t="n"/>
+      <c r="T16" s="5" t="n"/>
+      <c r="U16" s="5" t="n"/>
+      <c r="V16" s="5" t="n"/>
+      <c r="W16" s="5" t="n"/>
+      <c r="X16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  지체상금률</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>1일 하도급대금의 0.5/1,000</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="5" t="n"/>
+      <c r="Q17" s="5" t="n"/>
+      <c r="R17" s="5" t="n"/>
+      <c r="S17" s="5" t="n"/>
+      <c r="T17" s="5" t="n"/>
+      <c r="U17" s="5" t="n"/>
+      <c r="V17" s="5" t="n"/>
+      <c r="W17" s="5" t="n"/>
+      <c r="X17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  하자담보책임기간</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>준공일부터 2년</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
+      <c r="Q18" s="5" t="n"/>
+      <c r="R18" s="5" t="n"/>
+      <c r="S18" s="5" t="n"/>
+      <c r="T18" s="5" t="n"/>
+      <c r="U18" s="5" t="n"/>
+      <c r="V18" s="5" t="n"/>
+      <c r="W18" s="5" t="n"/>
+      <c r="X18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="6" customHeight="1"/>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>원사업자(이하 「갑」)와 수급사업자(이하 「을」)는 위 공사에 관하여 다음과 같이 하도급계약을 체결한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="6" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>제1조 (위탁 내용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="43.5" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>갑은 위 공사 중 별첨 내역서에 적은 부분을 을에게 위탁하고, 을은 설계도서·시방서 및 이 계약에 따라 이를 시공한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="4" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>제2조 (하도급대금)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>하도급대금은 위에 적은 금액으로 하며 부가가치세의 포함 여부는 위 표에 따른다. 갑은 정당한 사유 없이 하도급대금을 부당하게 감액하지 아니한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="4" customHeight="1"/>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>제3조 (대금의 지급)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>갑은 목적물의 수령일부터 위 지급기한 안에 하도급대금을 지급한다. 어음으로 지급하는 경우 만기는 관계 법령이 정한 기간을 넘지 아니하며, 그 기간을 넘는 부분에 대하여는 법정 할인료를 지급한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="4" customHeight="1"/>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>제4조 (발주자로부터 받은 대금의 지급)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="43.5" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>갑이 발주자로부터 기성금 또는 준공금을 받은 때에는 그 내용과 비율에 따라 정해진 기간 안에 을에게 지급한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="4" customHeight="1"/>
+    <row r="34" ht="6.333333333333333" customHeight="1"/>
+    <row r="35" ht="6.333333333333333" customHeight="1"/>
+    <row r="36" ht="6.333333333333333" customHeight="1"/>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>제5조 (검사)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="43.5" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>갑은 을이 시공을 마친 부분에 대하여 위 표에 적은 방법과 시기에 따라 검사하고 그 결과를 을에게 서면으로 통지한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="4" customHeight="1"/>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>제6조 (설계변경 등에 따른 조정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="43.5" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>설계변경·물가변동 등으로 원도급 계약금액이 조정된 때에는 갑은 그 내용과 비율에 따라 하도급대금을 조정한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="4" customHeight="1"/>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>제7조 (자재의 공급)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>갑이 자재를 공급하는 경우 그 품목·수량·단가·공급 시기를 별도로 정한다. 갑은 정당한 사유 없이 자기가 지정한 물품을 을에게 강제로 구입하게 하지 아니한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="4" customHeight="1"/>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>제8조 (안전보건)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>갑과 을은 산업안전보건 관계 법령을 지킨다. 갑은 안전보건 협의체를 운영하고 을은 이에 참여한다. 을은 소속 근로자의 산재보험·고용보험 가입 증명을 갑에게 제출한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="4" customHeight="1"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>제9조 (하도급대금 지급보증과 계약이행보증)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="43.5" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>갑은 하도급대금 지급보증서를 을에게 주고, 을은 계약이행보증서를 갑에게 준다. 다만 관계 법령에서 면제되는 경우에는 그러하지 아니하다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="4" customHeight="1"/>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>제10조 (재하도급의 제한)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="29" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>을은 갑의 서면 승낙 없이 이 계약의 공사를 다시 하도급할 수 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="4" customHeight="1"/>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>제11조 (지체상금)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="43.5" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>을의 책임 있는 사유로 공사가 지연된 때에는 지체일수에 하도급대금과 위 지체상금률을 곱한 금액을 갑에게 지급한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="4" customHeight="1"/>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>제12조 (하자담보책임)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="29" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>을은 목적물 인도일부터 위 기간 동안 시공상 하자를 무상으로 보수한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="4" customHeight="1"/>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>제13조 (계약의 해제·해지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="43.5" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>상대방이 이 계약을 위반하여 서면으로 최고하였음에도 상당한 기간 안에 시정하지 아니한 때에는 계약을 해제 또는 해지할 수 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="4" customHeight="1"/>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>제14조 (분쟁의 해결)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="43.5" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>이 계약에 관한 분쟁은 협의로 해결하되, 협의가 되지 아니한 때에는 하도급분쟁조정협의회의 조정 또는 관할 법원의 판결에 따른다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="4" customHeight="1"/>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>제15조 (특약사항)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="43.5" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>관급자재 인도 지연으로 늦어진 기간은 공사기간에 넣지 않는다. 그 밖의 사항은 건설업종 표준하도급계약서를 따른다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="4" customHeight="1"/>
+    <row r="70" ht="6" customHeight="1"/>
+    <row r="71" ht="7.291666666666686" customHeight="1"/>
+    <row r="72" ht="7.291666666666686" customHeight="1"/>
+    <row r="73" ht="7.291666666666686" customHeight="1"/>
+    <row r="74" ht="7.291666666666686" customHeight="1"/>
+    <row r="75" ht="34" customHeight="1">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>이 계약을 증명하기 위하여 계약서 2통을 작성하여 갑과 을이 각각 기명날인한 후 1통씩 보관한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="6" customHeight="1"/>
+    <row r="77" ht="24" customHeight="1">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n"/>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>상호(성명)</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="n"/>
+      <c r="G77" s="5" t="n"/>
+      <c r="H77" s="12" t="inlineStr">
+        <is>
+          <t>사업자등록번호</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="n"/>
+      <c r="J77" s="5" t="n"/>
+      <c r="K77" s="5" t="n"/>
+      <c r="L77" s="12" t="inlineStr">
+        <is>
+          <t>대표자</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="n"/>
+      <c r="N77" s="5" t="n"/>
+      <c r="O77" s="12" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="P77" s="5" t="n"/>
+      <c r="Q77" s="5" t="n"/>
+      <c r="R77" s="5" t="n"/>
+      <c r="S77" s="5" t="n"/>
+      <c r="T77" s="5" t="n"/>
+      <c r="U77" s="5" t="n"/>
+      <c r="V77" s="12" t="inlineStr">
+        <is>
+          <t>연락처</t>
+        </is>
+      </c>
+      <c r="W77" s="5" t="n"/>
+      <c r="X77" s="5" t="n"/>
+    </row>
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>갑</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n"/>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>예시건설(주)</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="13" t="inlineStr">
+        <is>
+          <t>000-00-00000</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="n"/>
+      <c r="J78" s="5" t="n"/>
+      <c r="K78" s="5" t="n"/>
+      <c r="L78" s="13" t="inlineStr">
+        <is>
+          <t>홍길동</t>
+        </is>
+      </c>
+      <c r="M78" s="5" t="n"/>
+      <c r="N78" s="5" t="n"/>
+      <c r="O78" s="14" t="inlineStr">
+        <is>
+          <t>가나시 마바로 45, 2층</t>
+        </is>
+      </c>
+      <c r="P78" s="5" t="n"/>
+      <c r="Q78" s="5" t="n"/>
+      <c r="R78" s="5" t="n"/>
+      <c r="S78" s="5" t="n"/>
+      <c r="T78" s="5" t="n"/>
+      <c r="U78" s="5" t="n"/>
+      <c r="V78" s="13" t="inlineStr">
+        <is>
+          <t>000-000-0000</t>
+        </is>
+      </c>
+      <c r="W78" s="5" t="n"/>
+      <c r="X78" s="5" t="n"/>
+    </row>
+    <row r="79" ht="32" customHeight="1">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>을</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n"/>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>(주)예시토건</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="n"/>
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="5" t="n"/>
+      <c r="G79" s="5" t="n"/>
+      <c r="H79" s="13" t="inlineStr">
+        <is>
+          <t>000-00-00000</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="n"/>
+      <c r="J79" s="5" t="n"/>
+      <c r="K79" s="5" t="n"/>
+      <c r="L79" s="13" t="inlineStr">
+        <is>
+          <t>나대표</t>
+        </is>
+      </c>
+      <c r="M79" s="5" t="n"/>
+      <c r="N79" s="5" t="n"/>
+      <c r="O79" s="14" t="inlineStr">
+        <is>
+          <t>다라시 가나로 12</t>
+        </is>
+      </c>
+      <c r="P79" s="5" t="n"/>
+      <c r="Q79" s="5" t="n"/>
+      <c r="R79" s="5" t="n"/>
+      <c r="S79" s="5" t="n"/>
+      <c r="T79" s="5" t="n"/>
+      <c r="U79" s="5" t="n"/>
+      <c r="V79" s="13" t="inlineStr">
+        <is>
+          <t>000-000-0000</t>
+        </is>
+      </c>
+      <c r="W79" s="5" t="n"/>
+      <c r="X79" s="5" t="n"/>
+    </row>
+    <row r="80" ht="6" customHeight="1"/>
+    <row r="81" ht="34" customHeight="1">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>※ 이 계약서는 일반 양식입니다. 실제 체결 전에 반드시 검토를 받으시고, 정부가 고시한 표준계약서가 있는 계약은 그 원문을 사용하시는 편이 안전합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="6" customHeight="1"/>
+    <row r="83" ht="10" customHeight="1"/>
+    <row r="84" ht="26" customHeight="1">
+      <c r="A84" s="15" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="85" ht="24" customHeight="1">
+      <c r="A85" s="16" t="inlineStr"/>
+      <c r="K85" s="17" t="inlineStr">
+        <is>
+          <t>갑 (원사업자)</t>
+        </is>
+      </c>
+      <c r="Q85" s="18" t="inlineStr">
+        <is>
+          <t>홍길동</t>
+        </is>
+      </c>
+      <c r="U85" s="19" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="24" customHeight="1">
+      <c r="A86" s="16" t="inlineStr"/>
+      <c r="K86" s="17" t="inlineStr">
+        <is>
+          <t>을 (수급사업자)</t>
+        </is>
+      </c>
+      <c r="Q86" s="18" t="inlineStr">
+        <is>
+          <t>나대표</t>
+        </is>
+      </c>
+      <c r="U86" s="19" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="6" customHeight="1"/>
+    <row r="89" ht="19.5" customHeight="1">
+      <c r="A89" s="20" t="inlineStr">
+        <is>
+          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="92">
+    <mergeCell ref="K85:P85"/>
+    <mergeCell ref="Q86:T86"/>
+    <mergeCell ref="G10:X10"/>
+    <mergeCell ref="A75:X75"/>
+    <mergeCell ref="G18:X18"/>
+    <mergeCell ref="K86:P86"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="A55:X55"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A32:X32"/>
+    <mergeCell ref="A29:X29"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A81:X81"/>
+    <mergeCell ref="A38:X38"/>
+    <mergeCell ref="A31:X31"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A58:X58"/>
+    <mergeCell ref="A40:X40"/>
+    <mergeCell ref="A67:X67"/>
+    <mergeCell ref="G12:X12"/>
+    <mergeCell ref="H79:K79"/>
+    <mergeCell ref="V78:X78"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="G7:X7"/>
+    <mergeCell ref="A25:X25"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A84:X84"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="U85:X85"/>
+    <mergeCell ref="A50:X50"/>
+    <mergeCell ref="A47:X47"/>
+    <mergeCell ref="O77:U77"/>
+    <mergeCell ref="A22:X22"/>
+    <mergeCell ref="G16:X16"/>
+    <mergeCell ref="A20:X20"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A28:X28"/>
+    <mergeCell ref="L77:N77"/>
+    <mergeCell ref="G9:X9"/>
+    <mergeCell ref="A44:X44"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A59:X59"/>
+    <mergeCell ref="G11:X11"/>
+    <mergeCell ref="A64:X64"/>
+    <mergeCell ref="A86:J86"/>
+    <mergeCell ref="L78:N78"/>
+    <mergeCell ref="A61:X61"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="O79:U79"/>
+    <mergeCell ref="A41:X41"/>
+    <mergeCell ref="G13:X13"/>
+    <mergeCell ref="A56:X56"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="L79:N79"/>
+    <mergeCell ref="G15:X15"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A53:X53"/>
+    <mergeCell ref="A62:X62"/>
+    <mergeCell ref="A68:X68"/>
+    <mergeCell ref="U86:X86"/>
+    <mergeCell ref="Q85:T85"/>
+    <mergeCell ref="G17:X17"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="V77:X77"/>
+    <mergeCell ref="A85:J85"/>
+    <mergeCell ref="A65:X65"/>
+    <mergeCell ref="H77:K77"/>
+    <mergeCell ref="G6:X6"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A37:X37"/>
+    <mergeCell ref="A46:X46"/>
+    <mergeCell ref="A89:X89"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A26:X26"/>
+    <mergeCell ref="G5:X5"/>
+    <mergeCell ref="O78:U78"/>
+    <mergeCell ref="G14:X14"/>
+    <mergeCell ref="H78:K78"/>
+    <mergeCell ref="A23:X23"/>
+    <mergeCell ref="A43:X43"/>
+    <mergeCell ref="A52:X52"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="V79:X79"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A49:X49"/>
+    <mergeCell ref="M1:X1"/>
+    <mergeCell ref="G8:X8"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/gy-hadogeup.xlsx
+++ b/web/public/forms/gy-hadogeup.xlsx
@@ -599,7 +599,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="21" t="inlineStr">

--- a/web/public/forms/gy-hadogeup.xlsx
+++ b/web/public/forms/gy-hadogeup.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공사 하도급계약서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'공사 하도급계약서'!$A$1:$X$87</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -139,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -198,9 +196,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -778,10 +773,7 @@
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="8">
-        <f>IF(N(G9)=0,"",G9-ROUND(G9/1.1,0))</f>
-        <v/>
-      </c>
+      <c r="G10" s="8" t="n"/>
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
@@ -1446,6 +1438,7 @@
       </c>
     </row>
     <row r="87" ht="6" customHeight="1"/>
+    <row r="88"/>
     <row r="89" ht="34" customHeight="1">
       <c r="A89" s="20" t="inlineStr">
         <is>
@@ -1560,1094 +1553,4 @@
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:X89"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.6" customWidth="1" min="1" max="1"/>
-    <col width="3.6" customWidth="1" min="2" max="2"/>
-    <col width="3.6" customWidth="1" min="3" max="3"/>
-    <col width="3.6" customWidth="1" min="4" max="4"/>
-    <col width="3.6" customWidth="1" min="5" max="5"/>
-    <col width="3.6" customWidth="1" min="6" max="6"/>
-    <col width="3.6" customWidth="1" min="7" max="7"/>
-    <col width="3.6" customWidth="1" min="8" max="8"/>
-    <col width="3.6" customWidth="1" min="9" max="9"/>
-    <col width="3.6" customWidth="1" min="10" max="10"/>
-    <col width="3.6" customWidth="1" min="11" max="11"/>
-    <col width="3.6" customWidth="1" min="12" max="12"/>
-    <col width="3.6" customWidth="1" min="13" max="13"/>
-    <col width="3.6" customWidth="1" min="14" max="14"/>
-    <col width="3.6" customWidth="1" min="15" max="15"/>
-    <col width="3.6" customWidth="1" min="16" max="16"/>
-    <col width="3.6" customWidth="1" min="17" max="17"/>
-    <col width="3.6" customWidth="1" min="18" max="18"/>
-    <col width="3.6" customWidth="1" min="19" max="19"/>
-    <col width="3.6" customWidth="1" min="20" max="20"/>
-    <col width="3.6" customWidth="1" min="21" max="21"/>
-    <col width="3.6" customWidth="1" min="22" max="22"/>
-    <col width="3.6" customWidth="1" min="23" max="23"/>
-    <col width="3.6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>공 사 하 도 급 계 약 서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  원도급 공사명</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  하도급 공사명</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사 중 구조물공(암거)</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공사 장소</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>가나시 다라동 123-4 일원</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
-      <c r="S7" s="5" t="n"/>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  하도급 공사기간</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>2026. 5. 1. ~ 2026. 10. 31.</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  하도급대금</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="7" t="n">
-        <v>285000000</v>
-      </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-      <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
-      <c r="S9" s="5" t="n"/>
-      <c r="T9" s="5" t="n"/>
-      <c r="U9" s="5" t="n"/>
-      <c r="V9" s="5" t="n"/>
-      <c r="W9" s="5" t="n"/>
-      <c r="X9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  부가가치세</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="8">
-        <f>IF(N(G9)=0,"",G9-ROUND(G9/1.1,0))</f>
-        <v/>
-      </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-      <c r="P10" s="5" t="n"/>
-      <c r="Q10" s="5" t="n"/>
-      <c r="R10" s="5" t="n"/>
-      <c r="S10" s="5" t="n"/>
-      <c r="T10" s="5" t="n"/>
-      <c r="U10" s="5" t="n"/>
-      <c r="V10" s="5" t="n"/>
-      <c r="W10" s="5" t="n"/>
-      <c r="X10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  선급금</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>원사업자가 받은 선금 비율만큼, 받은 날부터 15일 안에 지급</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-      <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="5" t="n"/>
-      <c r="R11" s="5" t="n"/>
-      <c r="S11" s="5" t="n"/>
-      <c r="T11" s="5" t="n"/>
-      <c r="U11" s="5" t="n"/>
-      <c r="V11" s="5" t="n"/>
-      <c r="W11" s="5" t="n"/>
-      <c r="X11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  기성 지급 주기</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>월 1회</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-      <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="5" t="n"/>
-      <c r="R12" s="5" t="n"/>
-      <c r="S12" s="5" t="n"/>
-      <c r="T12" s="5" t="n"/>
-      <c r="U12" s="5" t="n"/>
-      <c r="V12" s="5" t="n"/>
-      <c r="W12" s="5" t="n"/>
-      <c r="X12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  대금 지급기한</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>원사업자가 기성금을 받은 날부터 15일 안</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-      <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="5" t="n"/>
-      <c r="R13" s="5" t="n"/>
-      <c r="S13" s="5" t="n"/>
-      <c r="T13" s="5" t="n"/>
-      <c r="U13" s="5" t="n"/>
-      <c r="V13" s="5" t="n"/>
-      <c r="W13" s="5" t="n"/>
-      <c r="X13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  지급 방법(현금/어음)</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>현금(하도급지킴이)</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-      <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="5" t="n"/>
-      <c r="R14" s="5" t="n"/>
-      <c r="S14" s="5" t="n"/>
-      <c r="T14" s="5" t="n"/>
-      <c r="U14" s="5" t="n"/>
-      <c r="V14" s="5" t="n"/>
-      <c r="W14" s="5" t="n"/>
-      <c r="X14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  계약이행보증</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>하도급대금의 10% (보증서)</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="5" t="n"/>
-      <c r="S15" s="5" t="n"/>
-      <c r="T15" s="5" t="n"/>
-      <c r="U15" s="5" t="n"/>
-      <c r="V15" s="5" t="n"/>
-      <c r="W15" s="5" t="n"/>
-      <c r="X15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  하도급대금 지급보증</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>건설공제조합 지급보증서 교부</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-      <c r="P16" s="5" t="n"/>
-      <c r="Q16" s="5" t="n"/>
-      <c r="R16" s="5" t="n"/>
-      <c r="S16" s="5" t="n"/>
-      <c r="T16" s="5" t="n"/>
-      <c r="U16" s="5" t="n"/>
-      <c r="V16" s="5" t="n"/>
-      <c r="W16" s="5" t="n"/>
-      <c r="X16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  지체상금률</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>1일 하도급대금의 0.5/1,000</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-      <c r="P17" s="5" t="n"/>
-      <c r="Q17" s="5" t="n"/>
-      <c r="R17" s="5" t="n"/>
-      <c r="S17" s="5" t="n"/>
-      <c r="T17" s="5" t="n"/>
-      <c r="U17" s="5" t="n"/>
-      <c r="V17" s="5" t="n"/>
-      <c r="W17" s="5" t="n"/>
-      <c r="X17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  하자담보책임기간</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>준공일부터 2년</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-      <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="5" t="n"/>
-      <c r="R18" s="5" t="n"/>
-      <c r="S18" s="5" t="n"/>
-      <c r="T18" s="5" t="n"/>
-      <c r="U18" s="5" t="n"/>
-      <c r="V18" s="5" t="n"/>
-      <c r="W18" s="5" t="n"/>
-      <c r="X18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="6" customHeight="1"/>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>원사업자(이하 「갑」)와 수급사업자(이하 「을」)는 위 공사에 관하여 다음과 같이 하도급계약을 체결한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="6" customHeight="1"/>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>제1조 (위탁 내용)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="43.5" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>갑은 위 공사 중 별첨 내역서에 적은 부분을 을에게 위탁하고, 을은 설계도서·시방서 및 이 계약에 따라 이를 시공한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="4" customHeight="1"/>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>제2조 (하도급대금)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>하도급대금은 위에 적은 금액으로 하며 부가가치세의 포함 여부는 위 표에 따른다. 갑은 정당한 사유 없이 하도급대금을 부당하게 감액하지 아니한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="4" customHeight="1"/>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>제3조 (대금의 지급)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>갑은 목적물의 수령일부터 위 지급기한 안에 하도급대금을 지급한다. 어음으로 지급하는 경우 만기는 관계 법령이 정한 기간을 넘지 아니하며, 그 기간을 넘는 부분에 대하여는 법정 할인료를 지급한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="4" customHeight="1"/>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>제4조 (발주자로부터 받은 대금의 지급)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="43.5" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>갑이 발주자로부터 기성금 또는 준공금을 받은 때에는 그 내용과 비율에 따라 정해진 기간 안에 을에게 지급한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="4" customHeight="1"/>
-    <row r="34" ht="6.333333333333333" customHeight="1"/>
-    <row r="35" ht="6.333333333333333" customHeight="1"/>
-    <row r="36" ht="6.333333333333333" customHeight="1"/>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>제5조 (검사)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="43.5" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>갑은 을이 시공을 마친 부분에 대하여 위 표에 적은 방법과 시기에 따라 검사하고 그 결과를 을에게 서면으로 통지한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="4" customHeight="1"/>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>제6조 (설계변경 등에 따른 조정)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="43.5" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>설계변경·물가변동 등으로 원도급 계약금액이 조정된 때에는 갑은 그 내용과 비율에 따라 하도급대금을 조정한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="4" customHeight="1"/>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>제7조 (자재의 공급)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="58" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>갑이 자재를 공급하는 경우 그 품목·수량·단가·공급 시기를 별도로 정한다. 갑은 정당한 사유 없이 자기가 지정한 물품을 을에게 강제로 구입하게 하지 아니한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="4" customHeight="1"/>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>제8조 (안전보건)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="58" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>갑과 을은 산업안전보건 관계 법령을 지킨다. 갑은 안전보건 협의체를 운영하고 을은 이에 참여한다. 을은 소속 근로자의 산재보험·고용보험 가입 증명을 갑에게 제출한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="4" customHeight="1"/>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>제9조 (하도급대금 지급보증과 계약이행보증)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="43.5" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>갑은 하도급대금 지급보증서를 을에게 주고, 을은 계약이행보증서를 갑에게 준다. 다만 관계 법령에서 면제되는 경우에는 그러하지 아니하다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="4" customHeight="1"/>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>제10조 (재하도급의 제한)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="29" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>을은 갑의 서면 승낙 없이 이 계약의 공사를 다시 하도급할 수 없다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="4" customHeight="1"/>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>제11조 (지체상금)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="43.5" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>을의 책임 있는 사유로 공사가 지연된 때에는 지체일수에 하도급대금과 위 지체상금률을 곱한 금액을 갑에게 지급한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="4" customHeight="1"/>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>제12조 (하자담보책임)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="29" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>을은 목적물 인도일부터 위 기간 동안 시공상 하자를 무상으로 보수한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="4" customHeight="1"/>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>제13조 (계약의 해제·해지)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="43.5" customHeight="1">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t>상대방이 이 계약을 위반하여 서면으로 최고하였음에도 상당한 기간 안에 시정하지 아니한 때에는 계약을 해제 또는 해지할 수 있다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="4" customHeight="1"/>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>제14조 (분쟁의 해결)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="43.5" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t>이 계약에 관한 분쟁은 협의로 해결하되, 협의가 되지 아니한 때에는 하도급분쟁조정협의회의 조정 또는 관할 법원의 판결에 따른다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="4" customHeight="1"/>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>제15조 (특약사항)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="43.5" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t>관급자재 인도 지연으로 늦어진 기간은 공사기간에 넣지 않는다. 그 밖의 사항은 건설업종 표준하도급계약서를 따른다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="4" customHeight="1"/>
-    <row r="70" ht="6" customHeight="1"/>
-    <row r="71" ht="7.291666666666686" customHeight="1"/>
-    <row r="72" ht="7.291666666666686" customHeight="1"/>
-    <row r="73" ht="7.291666666666686" customHeight="1"/>
-    <row r="74" ht="7.291666666666686" customHeight="1"/>
-    <row r="75" ht="34" customHeight="1">
-      <c r="A75" s="9" t="inlineStr">
-        <is>
-          <t>이 계약을 증명하기 위하여 계약서 2통을 작성하여 갑과 을이 각각 기명날인한 후 1통씩 보관한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="6" customHeight="1"/>
-    <row r="77" ht="24" customHeight="1">
-      <c r="A77" s="12" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="n"/>
-      <c r="C77" s="12" t="inlineStr">
-        <is>
-          <t>상호(성명)</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="n"/>
-      <c r="E77" s="5" t="n"/>
-      <c r="F77" s="5" t="n"/>
-      <c r="G77" s="5" t="n"/>
-      <c r="H77" s="12" t="inlineStr">
-        <is>
-          <t>사업자등록번호</t>
-        </is>
-      </c>
-      <c r="I77" s="5" t="n"/>
-      <c r="J77" s="5" t="n"/>
-      <c r="K77" s="5" t="n"/>
-      <c r="L77" s="12" t="inlineStr">
-        <is>
-          <t>대표자</t>
-        </is>
-      </c>
-      <c r="M77" s="5" t="n"/>
-      <c r="N77" s="5" t="n"/>
-      <c r="O77" s="12" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="P77" s="5" t="n"/>
-      <c r="Q77" s="5" t="n"/>
-      <c r="R77" s="5" t="n"/>
-      <c r="S77" s="5" t="n"/>
-      <c r="T77" s="5" t="n"/>
-      <c r="U77" s="5" t="n"/>
-      <c r="V77" s="12" t="inlineStr">
-        <is>
-          <t>연락처</t>
-        </is>
-      </c>
-      <c r="W77" s="5" t="n"/>
-      <c r="X77" s="5" t="n"/>
-    </row>
-    <row r="78" ht="32" customHeight="1">
-      <c r="A78" s="13" t="inlineStr">
-        <is>
-          <t>갑</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="n"/>
-      <c r="C78" s="13" t="inlineStr">
-        <is>
-          <t>예시건설(주)</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="n"/>
-      <c r="E78" s="5" t="n"/>
-      <c r="F78" s="5" t="n"/>
-      <c r="G78" s="5" t="n"/>
-      <c r="H78" s="13" t="inlineStr">
-        <is>
-          <t>000-00-00000</t>
-        </is>
-      </c>
-      <c r="I78" s="5" t="n"/>
-      <c r="J78" s="5" t="n"/>
-      <c r="K78" s="5" t="n"/>
-      <c r="L78" s="13" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="M78" s="5" t="n"/>
-      <c r="N78" s="5" t="n"/>
-      <c r="O78" s="14" t="inlineStr">
-        <is>
-          <t>가나시 마바로 45, 2층</t>
-        </is>
-      </c>
-      <c r="P78" s="5" t="n"/>
-      <c r="Q78" s="5" t="n"/>
-      <c r="R78" s="5" t="n"/>
-      <c r="S78" s="5" t="n"/>
-      <c r="T78" s="5" t="n"/>
-      <c r="U78" s="5" t="n"/>
-      <c r="V78" s="13" t="inlineStr">
-        <is>
-          <t>000-000-0000</t>
-        </is>
-      </c>
-      <c r="W78" s="5" t="n"/>
-      <c r="X78" s="5" t="n"/>
-    </row>
-    <row r="79" ht="32" customHeight="1">
-      <c r="A79" s="13" t="inlineStr">
-        <is>
-          <t>을</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="n"/>
-      <c r="C79" s="13" t="inlineStr">
-        <is>
-          <t>(주)예시토건</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="n"/>
-      <c r="E79" s="5" t="n"/>
-      <c r="F79" s="5" t="n"/>
-      <c r="G79" s="5" t="n"/>
-      <c r="H79" s="13" t="inlineStr">
-        <is>
-          <t>000-00-00000</t>
-        </is>
-      </c>
-      <c r="I79" s="5" t="n"/>
-      <c r="J79" s="5" t="n"/>
-      <c r="K79" s="5" t="n"/>
-      <c r="L79" s="13" t="inlineStr">
-        <is>
-          <t>나대표</t>
-        </is>
-      </c>
-      <c r="M79" s="5" t="n"/>
-      <c r="N79" s="5" t="n"/>
-      <c r="O79" s="14" t="inlineStr">
-        <is>
-          <t>다라시 가나로 12</t>
-        </is>
-      </c>
-      <c r="P79" s="5" t="n"/>
-      <c r="Q79" s="5" t="n"/>
-      <c r="R79" s="5" t="n"/>
-      <c r="S79" s="5" t="n"/>
-      <c r="T79" s="5" t="n"/>
-      <c r="U79" s="5" t="n"/>
-      <c r="V79" s="13" t="inlineStr">
-        <is>
-          <t>000-000-0000</t>
-        </is>
-      </c>
-      <c r="W79" s="5" t="n"/>
-      <c r="X79" s="5" t="n"/>
-    </row>
-    <row r="80" ht="6" customHeight="1"/>
-    <row r="81" ht="34" customHeight="1">
-      <c r="A81" s="9" t="inlineStr">
-        <is>
-          <t>※ 이 계약서는 일반 양식입니다. 실제 체결 전에 반드시 검토를 받으시고, 정부가 고시한 표준계약서가 있는 계약은 그 원문을 사용하시는 편이 안전합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="6" customHeight="1"/>
-    <row r="83" ht="10" customHeight="1"/>
-    <row r="84" ht="26" customHeight="1">
-      <c r="A84" s="15" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="85" ht="24" customHeight="1">
-      <c r="A85" s="16" t="inlineStr"/>
-      <c r="K85" s="17" t="inlineStr">
-        <is>
-          <t>갑 (원사업자)</t>
-        </is>
-      </c>
-      <c r="Q85" s="18" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="U85" s="19" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="24" customHeight="1">
-      <c r="A86" s="16" t="inlineStr"/>
-      <c r="K86" s="17" t="inlineStr">
-        <is>
-          <t>을 (수급사업자)</t>
-        </is>
-      </c>
-      <c r="Q86" s="18" t="inlineStr">
-        <is>
-          <t>나대표</t>
-        </is>
-      </c>
-      <c r="U86" s="19" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="6" customHeight="1"/>
-    <row r="89" ht="19.5" customHeight="1">
-      <c r="A89" s="20" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="92">
-    <mergeCell ref="K85:P85"/>
-    <mergeCell ref="Q86:T86"/>
-    <mergeCell ref="G10:X10"/>
-    <mergeCell ref="A75:X75"/>
-    <mergeCell ref="G18:X18"/>
-    <mergeCell ref="K86:P86"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="A55:X55"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A32:X32"/>
-    <mergeCell ref="A29:X29"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A81:X81"/>
-    <mergeCell ref="A38:X38"/>
-    <mergeCell ref="A31:X31"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A58:X58"/>
-    <mergeCell ref="A40:X40"/>
-    <mergeCell ref="A67:X67"/>
-    <mergeCell ref="G12:X12"/>
-    <mergeCell ref="H79:K79"/>
-    <mergeCell ref="V78:X78"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="G7:X7"/>
-    <mergeCell ref="A25:X25"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A84:X84"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="U85:X85"/>
-    <mergeCell ref="A50:X50"/>
-    <mergeCell ref="A47:X47"/>
-    <mergeCell ref="O77:U77"/>
-    <mergeCell ref="A22:X22"/>
-    <mergeCell ref="G16:X16"/>
-    <mergeCell ref="A20:X20"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A28:X28"/>
-    <mergeCell ref="L77:N77"/>
-    <mergeCell ref="G9:X9"/>
-    <mergeCell ref="A44:X44"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A59:X59"/>
-    <mergeCell ref="G11:X11"/>
-    <mergeCell ref="A64:X64"/>
-    <mergeCell ref="A86:J86"/>
-    <mergeCell ref="L78:N78"/>
-    <mergeCell ref="A61:X61"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="O79:U79"/>
-    <mergeCell ref="A41:X41"/>
-    <mergeCell ref="G13:X13"/>
-    <mergeCell ref="A56:X56"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="L79:N79"/>
-    <mergeCell ref="G15:X15"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A53:X53"/>
-    <mergeCell ref="A62:X62"/>
-    <mergeCell ref="A68:X68"/>
-    <mergeCell ref="U86:X86"/>
-    <mergeCell ref="Q85:T85"/>
-    <mergeCell ref="G17:X17"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="V77:X77"/>
-    <mergeCell ref="A85:J85"/>
-    <mergeCell ref="A65:X65"/>
-    <mergeCell ref="H77:K77"/>
-    <mergeCell ref="G6:X6"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A37:X37"/>
-    <mergeCell ref="A46:X46"/>
-    <mergeCell ref="A89:X89"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A26:X26"/>
-    <mergeCell ref="G5:X5"/>
-    <mergeCell ref="O78:U78"/>
-    <mergeCell ref="G14:X14"/>
-    <mergeCell ref="H78:K78"/>
-    <mergeCell ref="A23:X23"/>
-    <mergeCell ref="A43:X43"/>
-    <mergeCell ref="A52:X52"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="V79:X79"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A49:X49"/>
-    <mergeCell ref="M1:X1"/>
-    <mergeCell ref="G8:X8"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/gy-hadogeup.xlsx
+++ b/web/public/forms/gy-hadogeup.xlsx
@@ -594,7 +594,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
